--- a/data/performance/daily/signal_list_2026-05-22.xlsx
+++ b/data/performance/daily/signal_list_2026-05-22.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 41.7%  (5W / 7L of 12 evaluated)</t>
+          <t>Win Rate: 50.0%  (6W / 6L of 12 evaluated)</t>
         </is>
       </c>
     </row>
@@ -493,7 +493,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2600</v>
+        <v>2570</v>
       </c>
       <c r="D5" t="n">
         <v>2630</v>
@@ -553,10 +553,10 @@
         <v>2670</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2.69</v>
+        <v>3.89</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.15</v>
+        <v>2.33</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1500</v>
+        <v>1505</v>
       </c>
       <c r="D6" t="n">
         <v>1495</v>
@@ -595,10 +595,10 @@
         <v>1505</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.33</v>
+        <v>-0.66</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="D9" t="n">
         <v>120</v>
@@ -721,10 +721,10 @@
         <v>167</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>39.17</v>
+        <v>18.44</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0</v>
+        <v>-14.89</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D10" t="n">
         <v>164</v>
@@ -763,10 +763,10 @@
         <v>167</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D13" t="n">
         <v>234</v>
@@ -889,10 +889,10 @@
         <v>240</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4.35</v>
+        <v>5.26</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.74</v>
+        <v>2.63</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D14" t="n">
         <v>258</v>
@@ -931,10 +931,10 @@
         <v>274</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.74</v>
+        <v>1.48</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-5.15</v>
+        <v>-4.44</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D15" t="n">
         <v>408</v>
@@ -973,10 +973,10 @@
         <v>414</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.49</v>
+        <v>1.47</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.97</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D16" t="n">
         <v>496</v>
@@ -1015,14 +1015,14 @@
         <v>525</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
+        <v>3.33</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Prev</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">

--- a/data/performance/daily/signal_list_2026-05-22.xlsx
+++ b/data/performance/daily/signal_list_2026-05-22.xlsx
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -469,14 +469,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Swing Signal List — 2026-05-22</t>
+          <t>Swing — Review sesi market 2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 50.0%  (6W / 6L of 12 evaluated)</t>
+          <t>Win Rate: 36.4%  (4W / 7L of 11 evaluated)</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>JPFA.JK</t>
+          <t>APIC.JK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,28 +544,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2570</v>
+        <v>1570</v>
       </c>
       <c r="D5" t="n">
-        <v>2630</v>
+        <v>1345</v>
       </c>
       <c r="E5" t="n">
-        <v>2670</v>
+        <v>1635</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3.89</v>
+        <v>4.14</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>2.33</v>
+        <v>-14.33</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MAPI.JK</t>
+          <t>DMAS.JK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -586,28 +586,28 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1505</v>
+        <v>150</v>
       </c>
       <c r="D6" t="n">
-        <v>1495</v>
+        <v>151</v>
       </c>
       <c r="E6" t="n">
-        <v>1505</v>
+        <v>152</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.66</v>
+        <v>0.67</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -619,7 +619,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UNIC.JK</t>
+          <t>GGRM.JK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -628,28 +628,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14600</v>
+        <v>16200</v>
       </c>
       <c r="D7" t="n">
-        <v>15125</v>
+        <v>15800</v>
       </c>
       <c r="E7" t="n">
-        <v>15400</v>
+        <v>16200</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>5.48</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.6</v>
+        <v>-2.47</v>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRDA.JK</t>
+          <t>MAPI.JK</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -670,28 +670,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2510</v>
+        <v>1485</v>
       </c>
       <c r="D8" t="n">
-        <v>2550</v>
+        <v>1505</v>
       </c>
       <c r="E8" t="n">
-        <v>2590</v>
+        <v>1505</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>3.19</v>
+        <v>1.35</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
+        <v>1.35</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LCKM.JK</t>
+          <t>PRDA.JK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,28 +712,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>141</v>
+        <v>2550</v>
       </c>
       <c r="D9" t="n">
-        <v>120</v>
+        <v>2510</v>
       </c>
       <c r="E9" t="n">
-        <v>167</v>
+        <v>2540</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>18.44</v>
+        <v>-0.39</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-14.89</v>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
+        <v>-1.57</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -745,7 +745,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KJEN.JK</t>
+          <t>MARK.JK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -754,28 +754,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>165</v>
+        <v>795</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>810</v>
       </c>
       <c r="E10" t="n">
-        <v>167</v>
+        <v>810</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.21</v>
+        <v>1.89</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.61</v>
+        <v>1.89</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -787,7 +787,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GGRP.JK</t>
+          <t>MORA.JK</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -796,28 +796,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>328</v>
+        <v>6500</v>
       </c>
       <c r="D11" t="n">
-        <v>326</v>
+        <v>6700</v>
       </c>
       <c r="E11" t="n">
-        <v>334</v>
+        <v>7100</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.83</v>
+        <v>9.23</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.61</v>
+        <v>3.08</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>W</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -838,28 +838,28 @@
         </is>
       </c>
       <c r="C12" t="n">
+        <v>40</v>
+      </c>
+      <c r="D12" t="n">
         <v>36</v>
       </c>
-      <c r="D12" t="n">
-        <v>37</v>
-      </c>
       <c r="E12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>5.56</v>
+        <v>-10</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>2.78</v>
+        <v>-10</v>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UVCR.JK</t>
+          <t>BSML.JK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -880,28 +880,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>228</v>
+        <v>416</v>
       </c>
       <c r="D13" t="n">
-        <v>234</v>
+        <v>408</v>
       </c>
       <c r="E13" t="n">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>5.26</v>
+        <v>0.96</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.63</v>
+        <v>-1.92</v>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>L</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -913,7 +913,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BOBA.JK</t>
+          <t>PACK.JK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -922,28 +922,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="D14" t="n">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="E14" t="n">
-        <v>274</v>
+        <v>310</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.48</v>
+        <v>2.65</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.44</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
+        <v>-6.62</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -955,7 +955,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BSML.JK</t>
+          <t>ASPR.JK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -964,73 +964,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>408</v>
+        <v>338</v>
       </c>
       <c r="D15" t="n">
-        <v>408</v>
+        <v>288</v>
       </c>
       <c r="E15" t="n">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.47</v>
+        <v>11.83</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
+        <v>-14.79</v>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>evaluated</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>HBAT.JK</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>PRE_MARKUP</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>480</v>
-      </c>
-      <c r="D16" t="n">
-        <v>496</v>
-      </c>
-      <c r="E16" t="n">
-        <v>525</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>9.380000000000001</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1065,7 +1023,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Scalping Signal List — 2026-05-22</t>
+          <t>Scalping — Review sesi market 2026-05-22</t>
         </is>
       </c>
     </row>

--- a/data/performance/daily/signal_list_2026-05-22.xlsx
+++ b/data/performance/daily/signal_list_2026-05-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-22.xlsx
+++ b/data/performance/daily/signal_list_2026-05-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-05-22.xlsx
+++ b/data/performance/daily/signal_list_2026-05-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -55,12 +55,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -560,15 +566,20 @@
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>-2.47</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>-1.57</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -768,17 +799,22 @@
       <c r="G10" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -810,17 +846,22 @@
       <c r="G11" s="4" t="n">
         <v>3.08</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -896,15 +942,20 @@
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -938,15 +989,20 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -980,15 +1036,20 @@
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1005,7 +1066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1015,9 +1076,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1047,7 +1109,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1072,15 +1134,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>

--- a/data/performance/daily/signal_list_2026-05-22.xlsx
+++ b/data/performance/daily/signal_list_2026-05-22.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>1570</v>
       </c>
       <c r="D5" t="n">
+        <v>1555</v>
+      </c>
+      <c r="E5" t="n">
         <v>1345</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>1635</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>4.14</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>-14.33</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I5" s="6" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -603,30 +612,33 @@
         <v>151</v>
       </c>
       <c r="E6" t="n">
+        <v>151</v>
+      </c>
+      <c r="F6" t="n">
         <v>152</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.33</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>0.67</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>16200</v>
       </c>
       <c r="D7" t="n">
+        <v>16200</v>
+      </c>
+      <c r="E7" t="n">
         <v>15800</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>16200</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-2.47</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>1485</v>
       </c>
       <c r="D8" t="n">
-        <v>1505</v>
+        <v>1495</v>
       </c>
       <c r="E8" t="n">
         <v>1505</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>1.35</v>
+      <c r="F8" t="n">
+        <v>1505</v>
       </c>
       <c r="G8" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>2550</v>
       </c>
       <c r="D9" t="n">
+        <v>2530</v>
+      </c>
+      <c r="E9" t="n">
         <v>2510</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2540</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-1.57</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>795</v>
       </c>
       <c r="D10" t="n">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="E10" t="n">
         <v>810</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>1.89</v>
+      <c r="F10" t="n">
+        <v>810</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>6500</v>
       </c>
       <c r="D11" t="n">
+        <v>6550</v>
+      </c>
+      <c r="E11" t="n">
         <v>6700</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>7100</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>9.23</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>3.08</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -887,28 +914,31 @@
       <c r="E12" t="n">
         <v>36</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>-10</v>
+      <c r="F12" t="n">
+        <v>36</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>-10</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>416</v>
       </c>
       <c r="D13" t="n">
+        <v>418</v>
+      </c>
+      <c r="E13" t="n">
         <v>408</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>420</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>0.96</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="J13" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>302</v>
       </c>
       <c r="D14" t="n">
+        <v>300</v>
+      </c>
+      <c r="E14" t="n">
         <v>282</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>310</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>2.65</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-6.62</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="J14" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>338</v>
       </c>
       <c r="D15" t="n">
+        <v>318</v>
+      </c>
+      <c r="E15" t="n">
         <v>288</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>378</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>11.83</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>-14.79</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="J15" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1066,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1074,12 +1113,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1109,45 +1149,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
